--- a/tutorials/Alzheimer.xlsx
+++ b/tutorials/Alzheimer.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="923" uniqueCount="82">
   <si>
     <t>ADAS-cog-13</t>
   </si>
@@ -139,6 +139,15 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Systemic inflammation</t>
+  </si>
+  <si>
+    <t>Healthy dietary patterns</t>
+  </si>
+  <si>
+    <t>Neuroinflammation</t>
+  </si>
+  <si>
     <t>From</t>
   </si>
   <si>
@@ -169,9 +178,6 @@
     <t>Cerebral endothelial dysfunction</t>
   </si>
   <si>
-    <t>Neuroinflammation</t>
-  </si>
-  <si>
     <t>Head trauma</t>
   </si>
   <si>
@@ -190,9 +196,6 @@
     <t>Physical activity</t>
   </si>
   <si>
-    <t>Healthy dietary patterns</t>
-  </si>
-  <si>
     <t>Obesity</t>
   </si>
   <si>
@@ -205,9 +208,6 @@
     <t>Brain perfusion</t>
   </si>
   <si>
-    <t>Systemic inflammation</t>
-  </si>
-  <si>
     <t>Dyslipidaemia</t>
   </si>
   <si>
@@ -247,6 +247,9 @@
     <t>Tau burden</t>
   </si>
   <si>
+    <t>Equation</t>
+  </si>
+  <si>
     <t>stock</t>
   </si>
   <si>
@@ -257,6 +260,9 @@
   </si>
   <si>
     <t>constant</t>
+  </si>
+  <si>
+    <t>(1+tanh(-($+#1*Systemic inflammation*Systemic inflammation - #3*Healthy dietary patterns+#7*Systemic inflammation+#4*Oxidative stress + #5* Amyloid beta burden + #6*Head trauma)))/2</t>
   </si>
 </sst>
 </file>
@@ -264,13 +270,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
@@ -286,19 +298,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -344,17 +344,11 @@
   </cellStyleXfs>
   <cellXfs count="21">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -362,47 +356,53 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="7" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -706,27 +706,31 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="17" width="23.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="17" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="16" width="23.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="16" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="9" width="136.4335714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A1" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" s="12" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
+      <c r="A1" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>44</v>
+      <c r="C1" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>76</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
@@ -734,374 +738,407 @@
         <v>66</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" s="7">
         <v>0</v>
       </c>
       <c r="D2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5" customFormat="1" s="1">
+      <c r="A3" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>77</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5" customFormat="1" s="3">
-      <c r="A3" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>76</v>
       </c>
       <c r="C3" s="7">
         <v>0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" s="7">
         <v>0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="33">
       <c r="A5" s="11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" s="7">
         <v>0</v>
       </c>
-      <c r="D5" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D5" s="3"/>
+      <c r="E5" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A6" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>76</v>
+        <v>49</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>77</v>
       </c>
       <c r="C6" s="7">
         <v>0</v>
       </c>
-      <c r="D6" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D6" s="3"/>
+      <c r="E6" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A7" s="11" t="s">
         <v>69</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" s="7">
         <v>0</v>
       </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D7" s="3"/>
+      <c r="E7" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A8" s="11" t="s">
         <v>71</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" s="7">
         <v>0</v>
       </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D8" s="3"/>
+      <c r="E8" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A9" s="11" t="s">
         <v>65</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" s="7">
         <v>-1</v>
       </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D9" s="3"/>
+      <c r="E9" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A10" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C10" s="7">
         <v>-1</v>
       </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D10" s="3"/>
+      <c r="E10" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A11" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" s="7">
         <v>0</v>
       </c>
-      <c r="D11" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D11" s="3"/>
+      <c r="E11" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A12" s="11" t="s">
         <v>75</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C12" s="7">
         <v>0</v>
       </c>
-      <c r="D12" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="46.5" customFormat="1" s="3">
+      <c r="D12" s="3"/>
+      <c r="E12" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="46.5" customFormat="1" s="1">
       <c r="A13" s="11" t="s">
         <v>72</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" s="7">
         <v>0</v>
       </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D13" s="3"/>
+      <c r="E13" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A14" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>78</v>
+        <v>41</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="C14" s="7">
         <v>0</v>
       </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D14" s="3"/>
+      <c r="E14" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A15" s="11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
       </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D15" s="3"/>
+      <c r="E15" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A16" s="11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C16" s="7">
         <v>0</v>
       </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D16" s="3"/>
+      <c r="E16" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A17" s="11" t="s">
         <v>15</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" s="7">
         <v>0</v>
       </c>
-      <c r="D17" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D17" s="3"/>
+      <c r="E17" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A18" s="11" t="s">
         <v>63</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" s="7">
         <v>0</v>
       </c>
-      <c r="D18" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D18" s="3"/>
+      <c r="E18" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A19" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" s="19" t="s">
-        <v>78</v>
+        <v>57</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="C19" s="7">
         <v>0</v>
       </c>
-      <c r="D19" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D19" s="3"/>
+      <c r="E19" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A20" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>78</v>
+        <v>40</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="C20" s="7">
         <v>0</v>
       </c>
-      <c r="D20" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D20" s="3"/>
+      <c r="E20" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A21" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C21" s="7">
         <v>0</v>
       </c>
-      <c r="D21" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D21" s="3"/>
+      <c r="E21" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A22" s="11" t="s">
         <v>64</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22" s="7">
         <v>0</v>
       </c>
-      <c r="D22" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D22" s="3"/>
+      <c r="E22" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="36" customFormat="1" s="1">
       <c r="A23" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>78</v>
+        <v>42</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>79</v>
       </c>
       <c r="C23" s="7">
-        <v>0</v>
-      </c>
-      <c r="D23" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5" customFormat="1" s="3">
+        <v>-1</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A24" s="11" t="s">
         <v>68</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="7">
         <v>0</v>
       </c>
-      <c r="D24" s="2"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" s="7">
         <v>0</v>
       </c>
-      <c r="D25" s="2"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="11" t="s">
         <v>67</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C26" s="7">
         <v>0</v>
       </c>
-      <c r="D26" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D26" s="3"/>
+      <c r="E26" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A27" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>79</v>
+      <c r="B27" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="C27" s="7">
         <v>0</v>
       </c>
-      <c r="D27" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D27" s="3"/>
+      <c r="E27" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A28" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>79</v>
+      <c r="B28" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="C28" s="7">
         <v>0</v>
       </c>
-      <c r="D28" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D28" s="3"/>
+      <c r="E28" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A29" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>79</v>
+        <v>53</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="C29" s="7">
         <v>0</v>
       </c>
-      <c r="D29" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5" customFormat="1" s="3">
+      <c r="D29" s="3"/>
+      <c r="E29" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A30" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>79</v>
+        <v>54</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="C30" s="7">
         <v>0</v>
       </c>
-      <c r="D30" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="3">
+      <c r="D30" s="3"/>
+      <c r="E30" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A31" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>79</v>
+      <c r="B31" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="C31" s="7">
         <v>0</v>
       </c>
-      <c r="D31" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="3">
+      <c r="D31" s="3"/>
+      <c r="E31" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A32" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>79</v>
+      <c r="B32" s="11" t="s">
+        <v>80</v>
       </c>
       <c r="C32" s="7">
         <v>0</v>
       </c>
-      <c r="D32" s="2"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1116,462 +1153,462 @@
   <dimension ref="A1:G175"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="17" width="23.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="17" width="24.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="16" width="23.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="16" width="24.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A1" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="12" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A1" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="12" t="s">
+      <c r="C1" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>44</v>
+      <c r="F1" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D2" s="14"/>
       <c r="E2" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D3" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D3" s="14"/>
       <c r="E3" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="C4" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D4" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D4" s="14"/>
       <c r="E4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="13" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D5" s="14"/>
       <c r="E5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D6" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D6" s="14"/>
       <c r="E6" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D7" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D7" s="14"/>
       <c r="E7" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D8" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D8" s="14"/>
       <c r="E8" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D9" s="14"/>
       <c r="E9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>54</v>
-      </c>
       <c r="C10" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D10" s="14"/>
       <c r="E10" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D11" s="14"/>
       <c r="E11" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D12" s="14"/>
       <c r="E12" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D13" s="14"/>
       <c r="E13" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D14" s="14"/>
       <c r="E14" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D15" s="14"/>
       <c r="E15" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D16" s="14"/>
       <c r="E16" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D17" s="14"/>
       <c r="E17" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D18" s="14"/>
       <c r="E18" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="13" t="s">
         <v>63</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D19" s="14"/>
       <c r="E19" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D20" s="14"/>
       <c r="E20" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="13" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D21" s="14"/>
       <c r="E21" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D22" s="14"/>
       <c r="E22" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D23" s="14"/>
       <c r="E23" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D24" s="14"/>
       <c r="E24" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B25" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="C25" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D25" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D25" s="14"/>
       <c r="E25" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="13" t="s">
         <v>64</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D26" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D26" s="14"/>
       <c r="E26" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="13" t="s">
@@ -1581,31 +1618,31 @@
         <v>66</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D27" s="14"/>
       <c r="E27" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>66</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D28" s="14"/>
       <c r="E28" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="13" t="s">
@@ -1615,31 +1652,31 @@
         <v>66</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D29" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D29" s="14"/>
       <c r="E29" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>66</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D30" s="14"/>
       <c r="E30" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="13" t="s">
@@ -1649,65 +1686,65 @@
         <v>66</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D31" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D31" s="14"/>
       <c r="E31" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>66</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D32" s="14"/>
       <c r="E32" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B33" s="13" t="s">
         <v>66</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D33" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D33" s="14"/>
       <c r="E33" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>69</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D34" s="14"/>
       <c r="E34" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="13" t="s">
@@ -1717,14 +1754,14 @@
         <v>69</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D35" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D35" s="14"/>
       <c r="E35" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="13" t="s">
@@ -1734,14 +1771,14 @@
         <v>69</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D36" s="14"/>
       <c r="E36" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="13" t="s">
@@ -1751,48 +1788,48 @@
         <v>69</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D37" s="14"/>
       <c r="E37" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D38" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D38" s="14"/>
       <c r="E38" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B39" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D39" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D39" s="14"/>
       <c r="E39" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="13" t="s">
@@ -1802,99 +1839,99 @@
         <v>65</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D40" s="14"/>
       <c r="E40" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D41" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D41" s="14"/>
       <c r="E41" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>65</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D42" s="14"/>
       <c r="E42" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B43" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D43" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D43" s="14"/>
       <c r="E43" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D44" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D44" s="14"/>
       <c r="E44" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>63</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D45" s="14"/>
       <c r="E45" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="13" t="s">
@@ -1904,65 +1941,65 @@
         <v>63</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D46" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D46" s="14"/>
       <c r="E46" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B47" s="13" t="s">
         <v>63</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D47" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D47" s="14"/>
       <c r="E47" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>63</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D48" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D48" s="14"/>
       <c r="E48" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B49" s="13" t="s">
         <v>72</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D49" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D49" s="14"/>
       <c r="E49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
+      <c r="F49" s="14"/>
+      <c r="G49" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="13" t="s">
@@ -1972,14 +2009,14 @@
         <v>72</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D50" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D50" s="14"/>
       <c r="E50" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
+      <c r="F50" s="14"/>
+      <c r="G50" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="11" t="s">
@@ -1989,201 +2026,201 @@
         <v>72</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D51" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D51" s="14"/>
       <c r="E51" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15"/>
+      <c r="F51" s="14"/>
+      <c r="G51" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B52" s="13" t="s">
         <v>74</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D52" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D52" s="14"/>
       <c r="E52" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F52" s="14"/>
+      <c r="G52" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D53" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D53" s="14"/>
       <c r="E53" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F53" s="14"/>
+      <c r="G53" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="13" t="s">
         <v>73</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D54" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D54" s="14"/>
       <c r="E54" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F54" s="14"/>
+      <c r="G54" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B55" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D55" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D55" s="14"/>
       <c r="E55" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
+      <c r="F55" s="14"/>
+      <c r="G55" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D56" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D56" s="14"/>
       <c r="E56" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F56" s="15"/>
-      <c r="G56" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F56" s="14"/>
+      <c r="G56" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B57" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D57" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D57" s="14"/>
       <c r="E57" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F57" s="15"/>
-      <c r="G57" s="15"/>
+      <c r="F57" s="14"/>
+      <c r="G57" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="13" t="s">
         <v>73</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D58" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D58" s="14"/>
       <c r="E58" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F58" s="15"/>
-      <c r="G58" s="15"/>
+      <c r="F58" s="14"/>
+      <c r="G58" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D59" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D59" s="14"/>
       <c r="E59" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F59" s="14"/>
+      <c r="G59" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B60" s="13" t="s">
         <v>67</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D60" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D60" s="14"/>
       <c r="E60" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B61" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D61" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D61" s="14"/>
       <c r="E61" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F61" s="15"/>
-      <c r="G61" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F61" s="14"/>
+      <c r="G61" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B62" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D62" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D62" s="14"/>
       <c r="E62" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F62" s="15"/>
-      <c r="G62" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F62" s="14"/>
+      <c r="G62" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="13" t="s">
@@ -2193,65 +2230,65 @@
         <v>71</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D63" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D63" s="14"/>
       <c r="E63" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F63" s="15"/>
-      <c r="G63" s="15"/>
+      <c r="F63" s="14"/>
+      <c r="G63" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B64" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D64" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D64" s="14"/>
       <c r="E64" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F64" s="15"/>
-      <c r="G64" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F64" s="14"/>
+      <c r="G64" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B65" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D65" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D65" s="14"/>
       <c r="E65" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F65" s="15"/>
-      <c r="G65" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F65" s="14"/>
+      <c r="G65" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B66" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D66" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D66" s="14"/>
       <c r="E66" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F66" s="15"/>
-      <c r="G66" s="15"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="13" t="s">
@@ -2261,14 +2298,14 @@
         <v>71</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D67" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D67" s="14"/>
       <c r="E67" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
+      <c r="F67" s="14"/>
+      <c r="G67" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="13" t="s">
@@ -2278,48 +2315,48 @@
         <v>71</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D68" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D68" s="14"/>
       <c r="E68" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F68" s="15"/>
-      <c r="G68" s="15"/>
+      <c r="F68" s="14"/>
+      <c r="G68" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B69" s="13" t="s">
         <v>71</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D69" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D69" s="14"/>
       <c r="E69" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
+      <c r="F69" s="14"/>
+      <c r="G69" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B70" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D70" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D70" s="14"/>
       <c r="E70" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F70" s="15"/>
-      <c r="G70" s="15"/>
+      <c r="F70" s="14"/>
+      <c r="G70" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="13" t="s">
@@ -2329,150 +2366,150 @@
         <v>70</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D71" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D71" s="14"/>
       <c r="E71" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F71" s="15"/>
-      <c r="G71" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F71" s="14"/>
+      <c r="G71" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B72" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D72" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D72" s="14"/>
       <c r="E72" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F72" s="15"/>
-      <c r="G72" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F72" s="14"/>
+      <c r="G72" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B73" s="13" t="s">
         <v>70</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D73" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D73" s="14"/>
       <c r="E73" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F73" s="15"/>
-      <c r="G73" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F73" s="14"/>
+      <c r="G73" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D74" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D74" s="14"/>
       <c r="E74" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F74" s="14"/>
+      <c r="G74" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D75" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D75" s="14"/>
       <c r="E75" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F75" s="15"/>
-      <c r="G75" s="15"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D76" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D76" s="14"/>
       <c r="E76" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F76" s="15"/>
-      <c r="G76" s="15"/>
+      <c r="F76" s="14"/>
+      <c r="G76" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B77" s="13" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D77" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D77" s="14"/>
       <c r="E77" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F77" s="15"/>
-      <c r="G77" s="15"/>
+      <c r="F77" s="14"/>
+      <c r="G77" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="13" t="s">
         <v>64</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D78" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D78" s="14"/>
       <c r="E78" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
+      <c r="F78" s="14"/>
+      <c r="G78" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B79" s="13" t="s">
         <v>68</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D79" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D79" s="14"/>
       <c r="E79" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
+      <c r="F79" s="14"/>
+      <c r="G79" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="13" t="s">
@@ -2482,286 +2519,286 @@
         <v>68</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D80" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D80" s="14"/>
       <c r="E80" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F80" s="15"/>
-      <c r="G80" s="15"/>
+      <c r="F80" s="14"/>
+      <c r="G80" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B81" s="13" t="s">
         <v>68</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D81" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D81" s="14"/>
       <c r="E81" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F81" s="15"/>
-      <c r="G81" s="15"/>
+      <c r="F81" s="14"/>
+      <c r="G81" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B82" s="13" t="s">
         <v>68</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D82" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D82" s="14"/>
       <c r="E82" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F82" s="15"/>
-      <c r="G82" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F82" s="14"/>
+      <c r="G82" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="13" t="s">
         <v>19</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D83" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D83" s="14"/>
       <c r="E83" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F83" s="15"/>
-      <c r="G83" s="15"/>
+      <c r="F83" s="14"/>
+      <c r="G83" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="13" t="s">
         <v>74</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D84" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D84" s="14"/>
       <c r="E84" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B85" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D85" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D85" s="14"/>
       <c r="E85" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F85" s="15"/>
-      <c r="G85" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F85" s="14"/>
+      <c r="G85" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C86" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D86" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D86" s="14"/>
       <c r="E86" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F86" s="15"/>
-      <c r="G86" s="15"/>
+      <c r="F86" s="14"/>
+      <c r="G86" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="13" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B87" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D87" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D87" s="14"/>
       <c r="E87" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F87" s="15"/>
-      <c r="G87" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="13" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C88" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D88" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D88" s="14"/>
       <c r="E88" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F88" s="15"/>
-      <c r="G88" s="15"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B89" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D89" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D89" s="14"/>
       <c r="E89" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F89" s="15"/>
-      <c r="G89" s="15"/>
+      <c r="F89" s="14"/>
+      <c r="G89" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C90" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D90" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D90" s="14"/>
       <c r="E90" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F90" s="15"/>
-      <c r="G90" s="15"/>
+      <c r="F90" s="14"/>
+      <c r="G90" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="13" t="s">
         <v>75</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D91" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D91" s="14"/>
       <c r="E91" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F91" s="15"/>
-      <c r="G91" s="15"/>
+      <c r="F91" s="14"/>
+      <c r="G91" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="13" t="s">
         <v>64</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C92" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D92" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D92" s="14"/>
       <c r="E92" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F92" s="15"/>
-      <c r="G92" s="15"/>
+      <c r="F92" s="14"/>
+      <c r="G92" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B93" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D93" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D93" s="14"/>
       <c r="E93" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C94" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D94" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D94" s="14"/>
       <c r="E94" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F94" s="15"/>
-      <c r="G94" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F94" s="14"/>
+      <c r="G94" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B95" s="13" t="s">
         <v>64</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D95" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D95" s="14"/>
       <c r="E95" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F95" s="15"/>
-      <c r="G95" s="15"/>
+      <c r="F95" s="14"/>
+      <c r="G95" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B96" s="13" t="s">
         <v>64</v>
       </c>
       <c r="C96" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D96" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D96" s="14"/>
       <c r="E96" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F96" s="15"/>
-      <c r="G96" s="15"/>
+      <c r="F96" s="14"/>
+      <c r="G96" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="13" t="s">
@@ -2771,14 +2808,14 @@
         <v>64</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D97" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D97" s="14"/>
       <c r="E97" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F97" s="15"/>
-      <c r="G97" s="15"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="13" t="s">
@@ -2788,541 +2825,541 @@
         <v>64</v>
       </c>
       <c r="C98" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D98" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D98" s="14"/>
       <c r="E98" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F98" s="15"/>
-      <c r="G98" s="15"/>
+      <c r="F98" s="14"/>
+      <c r="G98" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B99" s="13" t="s">
         <v>64</v>
       </c>
       <c r="C99" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D99" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D99" s="14"/>
       <c r="E99" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F99" s="15"/>
-      <c r="G99" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F99" s="14"/>
+      <c r="G99" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C100" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D100" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D100" s="14"/>
       <c r="E100" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F100" s="15"/>
-      <c r="G100" s="15"/>
+      <c r="F100" s="14"/>
+      <c r="G100" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="13" t="s">
         <v>73</v>
       </c>
       <c r="B101" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D101" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D101" s="14"/>
       <c r="E101" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F101" s="15"/>
-      <c r="G101" s="15"/>
+      <c r="F101" s="14"/>
+      <c r="G101" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C102" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D102" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D102" s="14"/>
       <c r="E102" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F102" s="15"/>
-      <c r="G102" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F102" s="14"/>
+      <c r="G102" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B103" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D103" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D103" s="14"/>
       <c r="E103" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F103" s="15"/>
-      <c r="G103" s="15"/>
+      <c r="F103" s="14"/>
+      <c r="G103" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B104" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B104" s="13" t="s">
-        <v>56</v>
-      </c>
       <c r="C104" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D104" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D104" s="14"/>
       <c r="E104" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F104" s="15"/>
-      <c r="G104" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F104" s="14"/>
+      <c r="G104" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B105" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C105" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D105" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D105" s="14"/>
       <c r="E105" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F105" s="15"/>
-      <c r="G105" s="15"/>
+      <c r="F105" s="14"/>
+      <c r="G105" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D106" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D106" s="14"/>
       <c r="E106" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F106" s="15"/>
-      <c r="G106" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F106" s="14"/>
+      <c r="G106" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D107" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D107" s="14"/>
       <c r="E107" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F107" s="15"/>
-      <c r="G107" s="15"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B108" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D108" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D108" s="14"/>
       <c r="E108" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F108" s="15"/>
-      <c r="G108" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F108" s="14"/>
+      <c r="G108" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B109" s="13" t="s">
         <v>19</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D109" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D109" s="14"/>
       <c r="E109" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F109" s="15"/>
-      <c r="G109" s="15"/>
+      <c r="F109" s="14"/>
+      <c r="G109" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="13" t="s">
         <v>73</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C110" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D110" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D110" s="14"/>
       <c r="E110" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F110" s="15"/>
-      <c r="G110" s="15"/>
+      <c r="F110" s="14"/>
+      <c r="G110" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="13" t="s">
         <v>73</v>
       </c>
       <c r="B111" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D111" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D111" s="14"/>
       <c r="E111" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F111" s="15"/>
-      <c r="G111" s="15"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D112" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D112" s="14"/>
       <c r="E112" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F112" s="15"/>
-      <c r="G112" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F112" s="14"/>
+      <c r="G112" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="13" t="s">
         <v>65</v>
       </c>
       <c r="B113" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C113" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D113" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D113" s="14"/>
       <c r="E113" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F113" s="15"/>
-      <c r="G113" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F113" s="14"/>
+      <c r="G113" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C114" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D114" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D114" s="14"/>
       <c r="E114" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F114" s="15"/>
-      <c r="G114" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F114" s="14"/>
+      <c r="G114" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="13" t="s">
         <v>66</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C115" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D115" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D115" s="14"/>
       <c r="E115" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F115" s="15"/>
-      <c r="G115" s="15"/>
+      <c r="F115" s="14"/>
+      <c r="G115" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="13" t="s">
         <v>67</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C116" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D116" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D116" s="14"/>
       <c r="E116" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F116" s="15"/>
-      <c r="G116" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F116" s="14"/>
+      <c r="G116" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
       <c r="A117" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B117" s="13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D117" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D117" s="14"/>
       <c r="E117" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F117" s="15"/>
-      <c r="G117" s="15"/>
+      <c r="F117" s="14"/>
+      <c r="G117" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
       <c r="A118" s="13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C118" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D118" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D118" s="14"/>
       <c r="E118" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F118" s="15"/>
-      <c r="G118" s="15"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
       <c r="A119" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B119" s="13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D119" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D119" s="14"/>
       <c r="E119" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F119" s="15"/>
-      <c r="G119" s="15"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
       <c r="A120" s="13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D120" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D120" s="14"/>
       <c r="E120" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F120" s="15"/>
-      <c r="G120" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F120" s="14"/>
+      <c r="G120" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
       <c r="A121" s="13" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D121" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D121" s="14"/>
       <c r="E121" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F121" s="15"/>
-      <c r="G121" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F121" s="14"/>
+      <c r="G121" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
       <c r="A122" s="13" t="s">
         <v>71</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C122" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D122" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D122" s="14"/>
       <c r="E122" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F122" s="15"/>
-      <c r="G122" s="15"/>
+      <c r="F122" s="14"/>
+      <c r="G122" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
       <c r="A123" s="13" t="s">
         <v>15</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D123" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D123" s="14"/>
       <c r="E123" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F123" s="15"/>
-      <c r="G123" s="15"/>
+      <c r="F123" s="14"/>
+      <c r="G123" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
       <c r="A124" s="13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D124" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D124" s="14"/>
       <c r="E124" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F124" s="15"/>
-      <c r="G124" s="15"/>
+      <c r="F124" s="14"/>
+      <c r="G124" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
       <c r="A125" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B125" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B125" s="13" t="s">
         <v>75</v>
       </c>
       <c r="C125" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D125" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D125" s="14"/>
       <c r="E125" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F125" s="15"/>
-      <c r="G125" s="15"/>
+        <v>51</v>
+      </c>
+      <c r="F125" s="14"/>
+      <c r="G125" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
       <c r="A126" s="13" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B126" s="13" t="s">
         <v>75</v>
       </c>
       <c r="C126" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D126" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D126" s="14"/>
       <c r="E126" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F126" s="15"/>
-      <c r="G126" s="15"/>
+      <c r="F126" s="14"/>
+      <c r="G126" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
       <c r="A127" s="13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B127" s="13" t="s">
         <v>75</v>
       </c>
       <c r="C127" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D127" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D127" s="14"/>
       <c r="E127" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F127" s="15"/>
-      <c r="G127" s="15"/>
+      <c r="F127" s="14"/>
+      <c r="G127" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
       <c r="A128" s="13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B128" s="13" t="s">
         <v>75</v>
       </c>
       <c r="C128" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D128" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D128" s="14"/>
       <c r="E128" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F128" s="15"/>
-      <c r="G128" s="15"/>
+      <c r="F128" s="14"/>
+      <c r="G128" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
       <c r="A129" s="13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B129" s="13" t="s">
         <v>75</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D129" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D129" s="14"/>
       <c r="E129" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F129" s="15"/>
-      <c r="G129" s="15"/>
+      <c r="F129" s="14"/>
+      <c r="G129" s="14"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
       <c r="A130" s="13" t="s">
@@ -3332,419 +3369,419 @@
         <v>75</v>
       </c>
       <c r="C130" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D130" s="15"/>
+        <v>50</v>
+      </c>
+      <c r="D130" s="14"/>
       <c r="E130" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F130" s="15"/>
-      <c r="G130" s="15"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A131" s="16"/>
-      <c r="B131" s="16"/>
+      <c r="F130" s="14"/>
+      <c r="G130" s="14"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A131" s="15"/>
+      <c r="B131" s="15"/>
       <c r="C131" s="10"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="16"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A132" s="16"/>
-      <c r="B132" s="16"/>
+      <c r="D131" s="3"/>
+      <c r="E131" s="15"/>
+      <c r="F131" s="3"/>
+      <c r="G131" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A132" s="15"/>
+      <c r="B132" s="15"/>
       <c r="C132" s="10"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="16"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A133" s="16"/>
-      <c r="B133" s="16"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="15"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A133" s="15"/>
+      <c r="B133" s="15"/>
       <c r="C133" s="10"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="16"/>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A134" s="16"/>
-      <c r="B134" s="16"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="15"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A134" s="15"/>
+      <c r="B134" s="15"/>
       <c r="C134" s="10"/>
-      <c r="D134" s="2"/>
-      <c r="E134" s="16"/>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A135" s="16"/>
-      <c r="B135" s="16"/>
+      <c r="D134" s="3"/>
+      <c r="E134" s="15"/>
+      <c r="F134" s="3"/>
+      <c r="G134" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A135" s="15"/>
+      <c r="B135" s="15"/>
       <c r="C135" s="10"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="16"/>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A136" s="16"/>
-      <c r="B136" s="16"/>
+      <c r="D135" s="3"/>
+      <c r="E135" s="15"/>
+      <c r="F135" s="3"/>
+      <c r="G135" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A136" s="15"/>
+      <c r="B136" s="15"/>
       <c r="C136" s="10"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="16"/>
-      <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A137" s="16"/>
-      <c r="B137" s="16"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="15"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A137" s="15"/>
+      <c r="B137" s="15"/>
       <c r="C137" s="10"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="16"/>
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A138" s="16"/>
-      <c r="B138" s="16"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="15"/>
+      <c r="F137" s="3"/>
+      <c r="G137" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A138" s="15"/>
+      <c r="B138" s="15"/>
       <c r="C138" s="10"/>
-      <c r="D138" s="2"/>
-      <c r="E138" s="16"/>
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A139" s="16"/>
-      <c r="B139" s="16"/>
+      <c r="D138" s="3"/>
+      <c r="E138" s="15"/>
+      <c r="F138" s="3"/>
+      <c r="G138" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A139" s="15"/>
+      <c r="B139" s="15"/>
       <c r="C139" s="10"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="16"/>
-      <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A140" s="16"/>
-      <c r="B140" s="16"/>
+      <c r="D139" s="3"/>
+      <c r="E139" s="15"/>
+      <c r="F139" s="3"/>
+      <c r="G139" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A140" s="15"/>
+      <c r="B140" s="15"/>
       <c r="C140" s="10"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="16"/>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A141" s="16"/>
-      <c r="B141" s="16"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="15"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A141" s="15"/>
+      <c r="B141" s="15"/>
       <c r="C141" s="10"/>
-      <c r="D141" s="2"/>
-      <c r="E141" s="16"/>
-      <c r="F141" s="2"/>
-      <c r="G141" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A142" s="16"/>
-      <c r="B142" s="16"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="15"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A142" s="15"/>
+      <c r="B142" s="15"/>
       <c r="C142" s="10"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="16"/>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A143" s="16"/>
-      <c r="B143" s="16"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="15"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A143" s="15"/>
+      <c r="B143" s="15"/>
       <c r="C143" s="10"/>
-      <c r="D143" s="2"/>
-      <c r="E143" s="16"/>
-      <c r="F143" s="2"/>
-      <c r="G143" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A144" s="16"/>
-      <c r="B144" s="16"/>
+      <c r="D143" s="3"/>
+      <c r="E143" s="15"/>
+      <c r="F143" s="3"/>
+      <c r="G143" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A144" s="15"/>
+      <c r="B144" s="15"/>
       <c r="C144" s="10"/>
-      <c r="D144" s="2"/>
-      <c r="E144" s="16"/>
-      <c r="F144" s="2"/>
-      <c r="G144" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A145" s="16"/>
-      <c r="B145" s="16"/>
+      <c r="D144" s="3"/>
+      <c r="E144" s="15"/>
+      <c r="F144" s="3"/>
+      <c r="G144" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A145" s="15"/>
+      <c r="B145" s="15"/>
       <c r="C145" s="10"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="16"/>
-      <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A146" s="16"/>
-      <c r="B146" s="16"/>
+      <c r="D145" s="3"/>
+      <c r="E145" s="15"/>
+      <c r="F145" s="3"/>
+      <c r="G145" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A146" s="15"/>
+      <c r="B146" s="15"/>
       <c r="C146" s="10"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="16"/>
-      <c r="F146" s="2"/>
-      <c r="G146" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A147" s="16"/>
-      <c r="B147" s="16"/>
+      <c r="D146" s="3"/>
+      <c r="E146" s="15"/>
+      <c r="F146" s="3"/>
+      <c r="G146" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A147" s="15"/>
+      <c r="B147" s="15"/>
       <c r="C147" s="10"/>
-      <c r="D147" s="2"/>
-      <c r="E147" s="16"/>
-      <c r="F147" s="2"/>
-      <c r="G147" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A148" s="16"/>
-      <c r="B148" s="16"/>
+      <c r="D147" s="3"/>
+      <c r="E147" s="15"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A148" s="15"/>
+      <c r="B148" s="15"/>
       <c r="C148" s="10"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="16"/>
-      <c r="F148" s="2"/>
-      <c r="G148" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A149" s="16"/>
-      <c r="B149" s="16"/>
+      <c r="D148" s="3"/>
+      <c r="E148" s="15"/>
+      <c r="F148" s="3"/>
+      <c r="G148" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A149" s="15"/>
+      <c r="B149" s="15"/>
       <c r="C149" s="10"/>
-      <c r="D149" s="2"/>
-      <c r="E149" s="16"/>
-      <c r="F149" s="2"/>
-      <c r="G149" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A150" s="16"/>
-      <c r="B150" s="16"/>
+      <c r="D149" s="3"/>
+      <c r="E149" s="15"/>
+      <c r="F149" s="3"/>
+      <c r="G149" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A150" s="15"/>
+      <c r="B150" s="15"/>
       <c r="C150" s="10"/>
-      <c r="D150" s="2"/>
-      <c r="E150" s="16"/>
-      <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A151" s="16"/>
-      <c r="B151" s="16"/>
+      <c r="D150" s="3"/>
+      <c r="E150" s="15"/>
+      <c r="F150" s="3"/>
+      <c r="G150" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A151" s="15"/>
+      <c r="B151" s="15"/>
       <c r="C151" s="10"/>
-      <c r="D151" s="2"/>
-      <c r="E151" s="16"/>
-      <c r="F151" s="2"/>
-      <c r="G151" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A152" s="16"/>
-      <c r="B152" s="16"/>
+      <c r="D151" s="3"/>
+      <c r="E151" s="15"/>
+      <c r="F151" s="3"/>
+      <c r="G151" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A152" s="15"/>
+      <c r="B152" s="15"/>
       <c r="C152" s="10"/>
-      <c r="D152" s="2"/>
-      <c r="E152" s="16"/>
-      <c r="F152" s="2"/>
-      <c r="G152" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A153" s="16"/>
-      <c r="B153" s="16"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="15"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A153" s="15"/>
+      <c r="B153" s="15"/>
       <c r="C153" s="10"/>
-      <c r="D153" s="2"/>
-      <c r="E153" s="16"/>
-      <c r="F153" s="2"/>
-      <c r="G153" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A154" s="16"/>
-      <c r="B154" s="16"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="15"/>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A154" s="15"/>
+      <c r="B154" s="15"/>
       <c r="C154" s="10"/>
-      <c r="D154" s="2"/>
-      <c r="E154" s="16"/>
-      <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A155" s="16"/>
-      <c r="B155" s="16"/>
+      <c r="D154" s="3"/>
+      <c r="E154" s="15"/>
+      <c r="F154" s="3"/>
+      <c r="G154" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A155" s="15"/>
+      <c r="B155" s="15"/>
       <c r="C155" s="10"/>
-      <c r="D155" s="2"/>
-      <c r="E155" s="16"/>
-      <c r="F155" s="2"/>
-      <c r="G155" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A156" s="16"/>
-      <c r="B156" s="16"/>
+      <c r="D155" s="3"/>
+      <c r="E155" s="15"/>
+      <c r="F155" s="3"/>
+      <c r="G155" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A156" s="15"/>
+      <c r="B156" s="15"/>
       <c r="C156" s="10"/>
-      <c r="D156" s="2"/>
-      <c r="E156" s="16"/>
-      <c r="F156" s="2"/>
-      <c r="G156" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A157" s="16"/>
-      <c r="B157" s="16"/>
+      <c r="D156" s="3"/>
+      <c r="E156" s="15"/>
+      <c r="F156" s="3"/>
+      <c r="G156" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A157" s="15"/>
+      <c r="B157" s="15"/>
       <c r="C157" s="10"/>
-      <c r="D157" s="2"/>
-      <c r="E157" s="16"/>
-      <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A158" s="16"/>
-      <c r="B158" s="16"/>
+      <c r="D157" s="3"/>
+      <c r="E157" s="15"/>
+      <c r="F157" s="3"/>
+      <c r="G157" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A158" s="15"/>
+      <c r="B158" s="15"/>
       <c r="C158" s="10"/>
-      <c r="D158" s="2"/>
-      <c r="E158" s="16"/>
-      <c r="F158" s="2"/>
-      <c r="G158" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A159" s="16"/>
-      <c r="B159" s="16"/>
+      <c r="D158" s="3"/>
+      <c r="E158" s="15"/>
+      <c r="F158" s="3"/>
+      <c r="G158" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A159" s="15"/>
+      <c r="B159" s="15"/>
       <c r="C159" s="10"/>
-      <c r="D159" s="2"/>
-      <c r="E159" s="16"/>
-      <c r="F159" s="2"/>
-      <c r="G159" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A160" s="16"/>
-      <c r="B160" s="16"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="15"/>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A160" s="15"/>
+      <c r="B160" s="15"/>
       <c r="C160" s="10"/>
-      <c r="D160" s="2"/>
-      <c r="E160" s="16"/>
-      <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A161" s="16"/>
-      <c r="B161" s="16"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="15"/>
+      <c r="F160" s="3"/>
+      <c r="G160" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A161" s="15"/>
+      <c r="B161" s="15"/>
       <c r="C161" s="10"/>
-      <c r="D161" s="2"/>
-      <c r="E161" s="16"/>
-      <c r="F161" s="2"/>
-      <c r="G161" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A162" s="16"/>
-      <c r="B162" s="16"/>
+      <c r="D161" s="3"/>
+      <c r="E161" s="15"/>
+      <c r="F161" s="3"/>
+      <c r="G161" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A162" s="15"/>
+      <c r="B162" s="15"/>
       <c r="C162" s="10"/>
-      <c r="D162" s="2"/>
-      <c r="E162" s="16"/>
-      <c r="F162" s="2"/>
-      <c r="G162" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A163" s="16"/>
-      <c r="B163" s="16"/>
+      <c r="D162" s="3"/>
+      <c r="E162" s="15"/>
+      <c r="F162" s="3"/>
+      <c r="G162" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A163" s="15"/>
+      <c r="B163" s="15"/>
       <c r="C163" s="10"/>
-      <c r="D163" s="2"/>
-      <c r="E163" s="16"/>
-      <c r="F163" s="2"/>
-      <c r="G163" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A164" s="16"/>
-      <c r="B164" s="16"/>
+      <c r="D163" s="3"/>
+      <c r="E163" s="15"/>
+      <c r="F163" s="3"/>
+      <c r="G163" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A164" s="15"/>
+      <c r="B164" s="15"/>
       <c r="C164" s="10"/>
-      <c r="D164" s="2"/>
-      <c r="E164" s="16"/>
-      <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A165" s="16"/>
-      <c r="B165" s="16"/>
+      <c r="D164" s="3"/>
+      <c r="E164" s="15"/>
+      <c r="F164" s="3"/>
+      <c r="G164" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A165" s="15"/>
+      <c r="B165" s="15"/>
       <c r="C165" s="10"/>
-      <c r="D165" s="2"/>
-      <c r="E165" s="16"/>
-      <c r="F165" s="2"/>
-      <c r="G165" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A166" s="16"/>
-      <c r="B166" s="16"/>
+      <c r="D165" s="3"/>
+      <c r="E165" s="15"/>
+      <c r="F165" s="3"/>
+      <c r="G165" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A166" s="15"/>
+      <c r="B166" s="15"/>
       <c r="C166" s="10"/>
-      <c r="D166" s="2"/>
-      <c r="E166" s="16"/>
-      <c r="F166" s="2"/>
-      <c r="G166" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A167" s="16"/>
-      <c r="B167" s="16"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="15"/>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A167" s="15"/>
+      <c r="B167" s="15"/>
       <c r="C167" s="10"/>
-      <c r="D167" s="2"/>
-      <c r="E167" s="16"/>
-      <c r="F167" s="2"/>
-      <c r="G167" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A168" s="16"/>
-      <c r="B168" s="16"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="15"/>
+      <c r="F167" s="3"/>
+      <c r="G167" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A168" s="15"/>
+      <c r="B168" s="15"/>
       <c r="C168" s="10"/>
-      <c r="D168" s="2"/>
-      <c r="E168" s="16"/>
-      <c r="F168" s="2"/>
-      <c r="G168" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A169" s="16"/>
-      <c r="B169" s="16"/>
+      <c r="D168" s="3"/>
+      <c r="E168" s="15"/>
+      <c r="F168" s="3"/>
+      <c r="G168" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A169" s="15"/>
+      <c r="B169" s="15"/>
       <c r="C169" s="10"/>
-      <c r="D169" s="2"/>
-      <c r="E169" s="16"/>
-      <c r="F169" s="2"/>
-      <c r="G169" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A170" s="16"/>
-      <c r="B170" s="16"/>
+      <c r="D169" s="3"/>
+      <c r="E169" s="15"/>
+      <c r="F169" s="3"/>
+      <c r="G169" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A170" s="15"/>
+      <c r="B170" s="15"/>
       <c r="C170" s="10"/>
-      <c r="D170" s="2"/>
-      <c r="E170" s="16"/>
-      <c r="F170" s="2"/>
-      <c r="G170" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A171" s="16"/>
-      <c r="B171" s="16"/>
+      <c r="D170" s="3"/>
+      <c r="E170" s="15"/>
+      <c r="F170" s="3"/>
+      <c r="G170" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A171" s="15"/>
+      <c r="B171" s="15"/>
       <c r="C171" s="10"/>
-      <c r="D171" s="2"/>
-      <c r="E171" s="16"/>
-      <c r="F171" s="2"/>
-      <c r="G171" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A172" s="16"/>
-      <c r="B172" s="16"/>
+      <c r="D171" s="3"/>
+      <c r="E171" s="15"/>
+      <c r="F171" s="3"/>
+      <c r="G171" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A172" s="15"/>
+      <c r="B172" s="15"/>
       <c r="C172" s="10"/>
-      <c r="D172" s="2"/>
-      <c r="E172" s="16"/>
-      <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A173" s="16"/>
-      <c r="B173" s="16"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="15"/>
+      <c r="F172" s="3"/>
+      <c r="G172" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A173" s="15"/>
+      <c r="B173" s="15"/>
       <c r="C173" s="10"/>
-      <c r="D173" s="2"/>
-      <c r="E173" s="16"/>
-      <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A174" s="16"/>
-      <c r="B174" s="16"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="15"/>
+      <c r="F173" s="3"/>
+      <c r="G173" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A174" s="15"/>
+      <c r="B174" s="15"/>
       <c r="C174" s="10"/>
-      <c r="D174" s="2"/>
-      <c r="E174" s="16"/>
-      <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A175" s="16"/>
-      <c r="B175" s="16"/>
+      <c r="D174" s="3"/>
+      <c r="E174" s="15"/>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A175" s="15"/>
+      <c r="B175" s="15"/>
       <c r="C175" s="10"/>
-      <c r="D175" s="2"/>
-      <c r="E175" s="16"/>
-      <c r="F175" s="2"/>
-      <c r="G175" s="2"/>
+      <c r="D175" s="3"/>
+      <c r="E175" s="15"/>
+      <c r="F175" s="3"/>
+      <c r="G175" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3760,12 +3797,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A1" s="10" t="s">
         <v>36</v>
       </c>
@@ -3779,38 +3816,44 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>42</v>
+      </c>
       <c r="D2" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A3" s="2"/>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A3" s="3"/>
       <c r="B3" s="11"/>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A4" s="2"/>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A4" s="3"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A5" s="11"/>
       <c r="B5" s="11"/>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A6" s="2"/>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A6" s="3"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="3">
-      <c r="A7" s="2"/>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A7" s="3"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
@@ -3833,12 +3876,12 @@
     <col min="3" max="3" style="9" width="32.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -3849,7 +3892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A3" s="4" t="s">
         <v>3</v>
       </c>
@@ -3860,7 +3903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -3871,7 +3914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -3882,7 +3925,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A6" s="4" t="s">
         <v>3</v>
       </c>
@@ -3893,7 +3936,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
@@ -3904,7 +3947,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A8" s="4" t="s">
         <v>0</v>
       </c>
@@ -3915,7 +3958,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
@@ -3926,7 +3969,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
@@ -3937,7 +3980,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A11" s="4" t="s">
         <v>3</v>
       </c>
@@ -3948,7 +3991,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A12" s="4" t="s">
         <v>5</v>
       </c>
@@ -3959,7 +4002,7 @@
         <v>8</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
@@ -3970,7 +4013,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
@@ -3981,7 +4024,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A15" s="4" t="s">
         <v>3</v>
       </c>
@@ -3992,7 +4035,7 @@
         <v>10</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A16" s="4" t="s">
         <v>10</v>
       </c>
@@ -4003,7 +4046,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A17" s="4" t="s">
         <v>6</v>
       </c>
@@ -4014,7 +4057,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A18" s="4" t="s">
         <v>3</v>
       </c>
@@ -4025,7 +4068,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A19" s="4" t="s">
         <v>5</v>
       </c>
@@ -4036,7 +4079,7 @@
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A20" s="4" t="s">
         <v>7</v>
       </c>
@@ -4047,7 +4090,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A21" s="4" t="s">
         <v>8</v>
       </c>
@@ -4058,7 +4101,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A22" s="4" t="s">
         <v>11</v>
       </c>
@@ -4069,7 +4112,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A23" s="4" t="s">
         <v>13</v>
       </c>
@@ -4080,7 +4123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A24" s="4" t="s">
         <v>14</v>
       </c>
@@ -4091,7 +4134,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A25" s="4" t="s">
         <v>9</v>
       </c>
@@ -4102,7 +4145,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A26" s="4" t="s">
         <v>15</v>
       </c>
@@ -4113,7 +4156,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A27" s="4" t="s">
         <v>8</v>
       </c>
@@ -4124,7 +4167,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A28" s="4" t="s">
         <v>17</v>
       </c>
@@ -4135,7 +4178,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A29" s="4" t="s">
         <v>7</v>
       </c>
@@ -4146,7 +4189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A30" s="4" t="s">
         <v>11</v>
       </c>
@@ -4157,7 +4200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A31" s="4" t="s">
         <v>13</v>
       </c>
@@ -4168,7 +4211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A32" s="4" t="s">
         <v>19</v>
       </c>
@@ -4179,7 +4222,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A33" s="4" t="s">
         <v>20</v>
       </c>
@@ -4190,7 +4233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A34" s="4" t="s">
         <v>7</v>
       </c>
@@ -4201,7 +4244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A35" s="4" t="s">
         <v>12</v>
       </c>
@@ -4212,7 +4255,7 @@
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A36" s="4" t="s">
         <v>18</v>
       </c>
@@ -4223,7 +4266,7 @@
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A37" s="4" t="s">
         <v>22</v>
       </c>
@@ -4234,7 +4277,7 @@
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A38" s="4" t="s">
         <v>23</v>
       </c>
@@ -4245,7 +4288,7 @@
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A39" s="4" t="s">
         <v>2</v>
       </c>
@@ -4256,7 +4299,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A40" s="4" t="s">
         <v>8</v>
       </c>
@@ -4267,7 +4310,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A41" s="4" t="s">
         <v>10</v>
       </c>
@@ -4278,7 +4321,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A42" s="4" t="s">
         <v>13</v>
       </c>
@@ -4289,7 +4332,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A43" s="4" t="s">
         <v>10</v>
       </c>
@@ -4300,7 +4343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A44" s="4" t="s">
         <v>16</v>
       </c>
@@ -4311,7 +4354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A45" s="4" t="s">
         <v>24</v>
       </c>
@@ -4322,7 +4365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A46" s="4" t="s">
         <v>25</v>
       </c>
@@ -4333,7 +4376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A47" s="4" t="s">
         <v>13</v>
       </c>
@@ -4344,7 +4387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A48" s="4" t="s">
         <v>6</v>
       </c>
@@ -4355,7 +4398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A49" s="4" t="s">
         <v>26</v>
       </c>
@@ -4366,7 +4409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A50" s="4" t="s">
         <v>13</v>
       </c>
@@ -4377,7 +4420,7 @@
         <v>25</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A51" s="4" t="s">
         <v>7</v>
       </c>
@@ -4388,7 +4431,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A52" s="4" t="s">
         <v>16</v>
       </c>
@@ -4399,7 +4442,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A53" s="4" t="s">
         <v>18</v>
       </c>
@@ -4410,7 +4453,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A54" s="4" t="s">
         <v>21</v>
       </c>
@@ -4421,7 +4464,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A55" s="4" t="s">
         <v>17</v>
       </c>
@@ -4432,7 +4475,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A56" s="4" t="s">
         <v>22</v>
       </c>
@@ -4443,7 +4486,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A57" s="4" t="s">
         <v>27</v>
       </c>
@@ -4454,7 +4497,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A58" s="4" t="s">
         <v>19</v>
       </c>
@@ -4465,7 +4508,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A59" s="4" t="s">
         <v>20</v>
       </c>
@@ -4476,7 +4519,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A60" s="4" t="s">
         <v>23</v>
       </c>
@@ -4487,7 +4530,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A61" s="4" t="s">
         <v>7</v>
       </c>
@@ -4498,7 +4541,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A62" s="4" t="s">
         <v>12</v>
       </c>
@@ -4509,7 +4552,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A63" s="4" t="s">
         <v>16</v>
       </c>
@@ -4520,7 +4563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A64" s="4" t="s">
         <v>18</v>
       </c>
@@ -4531,7 +4574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A65" s="4" t="s">
         <v>22</v>
       </c>
@@ -4542,7 +4585,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A66" s="4" t="s">
         <v>28</v>
       </c>
@@ -4553,7 +4596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A67" s="4" t="s">
         <v>15</v>
       </c>
@@ -4564,7 +4607,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A68" s="4" t="s">
         <v>29</v>
       </c>
@@ -4575,7 +4618,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A69" s="4" t="s">
         <v>19</v>
       </c>
@@ -4586,7 +4629,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A70" s="4" t="s">
         <v>23</v>
       </c>
@@ -4597,7 +4640,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A71" s="4" t="s">
         <v>30</v>
       </c>
@@ -4608,7 +4651,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
@@ -4619,7 +4662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A73" s="4" t="s">
         <v>21</v>
       </c>
@@ -4630,7 +4673,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A74" s="4" t="s">
         <v>17</v>
       </c>
@@ -4641,7 +4684,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A75" s="4" t="s">
         <v>15</v>
       </c>
@@ -4652,7 +4695,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A76" s="4" t="s">
         <v>23</v>
       </c>
@@ -4663,7 +4706,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A77" s="4" t="s">
         <v>30</v>
       </c>
@@ -4674,7 +4717,7 @@
         <v>22</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A78" s="4" t="s">
         <v>0</v>
       </c>
@@ -4685,7 +4728,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A79" s="4" t="s">
         <v>13</v>
       </c>
@@ -4696,7 +4739,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A80" s="4" t="s">
         <v>14</v>
       </c>
@@ -4707,7 +4750,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A81" s="4" t="s">
         <v>32</v>
       </c>
@@ -4718,7 +4761,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A82" s="4" t="s">
         <v>7</v>
       </c>
@@ -4729,7 +4772,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A83" s="4" t="s">
         <v>8</v>
       </c>
@@ -4740,7 +4783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A84" s="4" t="s">
         <v>10</v>
       </c>
@@ -4751,7 +4794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A85" s="4" t="s">
         <v>12</v>
       </c>
@@ -4762,7 +4805,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A86" s="4" t="s">
         <v>9</v>
       </c>
@@ -4773,7 +4816,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A87" s="4" t="s">
         <v>15</v>
       </c>
@@ -4784,7 +4827,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A88" s="4" t="s">
         <v>29</v>
       </c>
@@ -4795,7 +4838,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A89" s="4" t="s">
         <v>3</v>
       </c>
@@ -4806,7 +4849,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A90" s="4" t="s">
         <v>20</v>
       </c>
@@ -4817,7 +4860,7 @@
         <v>14</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A91" s="4" t="s">
         <v>8</v>
       </c>
@@ -4828,7 +4871,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A92" s="4" t="s">
         <v>10</v>
       </c>
@@ -4839,7 +4882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A93" s="4" t="s">
         <v>11</v>
       </c>
@@ -4850,7 +4893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A94" s="4" t="s">
         <v>0</v>
       </c>
@@ -4861,7 +4904,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A95" s="4" t="s">
         <v>3</v>
       </c>
@@ -4872,7 +4915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A96" s="4" t="s">
         <v>7</v>
       </c>
@@ -4883,7 +4926,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A97" s="4" t="s">
         <v>8</v>
       </c>
@@ -4894,7 +4937,7 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A98" s="4" t="s">
         <v>7</v>
       </c>
@@ -4905,7 +4948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A99" s="4" t="s">
         <v>8</v>
       </c>
@@ -4916,7 +4959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A100" s="4" t="s">
         <v>11</v>
       </c>
@@ -4927,7 +4970,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A101" s="4" t="s">
         <v>9</v>
       </c>
@@ -4938,7 +4981,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A102" s="4" t="s">
         <v>3</v>
       </c>
@@ -4949,7 +4992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A103" s="4" t="s">
         <v>10</v>
       </c>
@@ -4960,7 +5003,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A104" s="4" t="s">
         <v>18</v>
       </c>
@@ -4971,7 +5014,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A105" s="4" t="s">
         <v>21</v>
       </c>
@@ -4982,7 +5025,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A106" s="4" t="s">
         <v>22</v>
       </c>
@@ -4993,7 +5036,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A107" s="4" t="s">
         <v>23</v>
       </c>
@@ -5004,7 +5047,7 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A108" s="4" t="s">
         <v>30</v>
       </c>
@@ -5015,78 +5058,78 @@
         <v>27</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
-      <c r="A109" s="1"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
-      <c r="A110" s="1"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
-      <c r="A111" s="1"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
-      <c r="A112" s="1"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
-      <c r="A113" s="1"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
-      <c r="A114" s="1"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
-      <c r="A115" s="1"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75" customFormat="1" s="3">
+    <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A109" s="2"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A110" s="2"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A111" s="2"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A112" s="2"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A113" s="2"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A114" s="2"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A115" s="2"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A116" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75" customFormat="1" s="3">
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A117" s="7">
         <v>23</v>
       </c>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
-      <c r="A118" s="1"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
-      <c r="A119" s="1"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75" customFormat="1" s="3">
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A118" s="2"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75" customFormat="1" s="1">
+      <c r="A119" s="2"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A120" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75" customFormat="1" s="3">
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A121" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tutorials/Alzheimer.xlsx
+++ b/tutorials/Alzheimer.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="Elements"/>
@@ -270,7 +270,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,7 +280,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -294,12 +294,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
@@ -342,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="16">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -362,47 +356,32 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="5" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="4" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="6" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -709,436 +688,436 @@
   <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="23.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="16" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="19" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="20" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="136.4335714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="12" width="23.005" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="12" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="136.4335714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="3" t="s">
         <v>76</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="2">
         <v>0</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="14"/>
+      <c r="E2" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="2">
         <v>0</v>
       </c>
       <c r="D3" s="3"/>
-      <c r="E3" s="14"/>
+      <c r="E3" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="2">
         <v>0</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="14"/>
+      <c r="E4" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="33">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="2">
         <v>0</v>
       </c>
       <c r="D5" s="3"/>
-      <c r="E5" s="14"/>
+      <c r="E5" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="2">
         <v>0</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="E6" s="14"/>
+      <c r="E6" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="2">
         <v>0</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="14"/>
+      <c r="E7" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="2">
         <v>0</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="14"/>
+      <c r="E8" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="2">
         <v>-1</v>
       </c>
       <c r="D9" s="3"/>
-      <c r="E9" s="14"/>
+      <c r="E9" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="2">
         <v>-1</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="14"/>
+      <c r="E10" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="2">
         <v>0</v>
       </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="14"/>
+      <c r="E11" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="2">
         <v>0</v>
       </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="46.5" customFormat="1" s="1">
-      <c r="A13" s="11" t="s">
+      <c r="E12" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="47.25" customFormat="1" s="1">
+      <c r="A13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="2">
         <v>0</v>
       </c>
       <c r="D13" s="3"/>
-      <c r="E13" s="14"/>
+      <c r="E13" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="2">
         <v>0</v>
       </c>
       <c r="D14" s="3"/>
-      <c r="E14" s="14"/>
+      <c r="E14" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="2">
         <v>1</v>
       </c>
       <c r="D15" s="3"/>
-      <c r="E15" s="14"/>
+      <c r="E15" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="2">
         <v>0</v>
       </c>
       <c r="D16" s="3"/>
-      <c r="E16" s="14"/>
+      <c r="E16" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="2">
         <v>0</v>
       </c>
       <c r="D17" s="3"/>
-      <c r="E17" s="14"/>
+      <c r="E17" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="2">
         <v>0</v>
       </c>
       <c r="D18" s="3"/>
-      <c r="E18" s="14"/>
+      <c r="E18" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="2">
         <v>0</v>
       </c>
       <c r="D19" s="3"/>
-      <c r="E19" s="14"/>
+      <c r="E19" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="2">
         <v>0</v>
       </c>
       <c r="D20" s="3"/>
-      <c r="E20" s="14"/>
+      <c r="E20" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="2">
         <v>0</v>
       </c>
       <c r="D21" s="3"/>
-      <c r="E21" s="14"/>
+      <c r="E21" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="2">
         <v>0</v>
       </c>
       <c r="D22" s="3"/>
-      <c r="E22" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="36" customFormat="1" s="1">
-      <c r="A23" s="11" t="s">
+      <c r="E22" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="33" customFormat="1" s="1">
+      <c r="A23" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="2">
         <v>-1</v>
       </c>
       <c r="D23" s="3"/>
-      <c r="E23" s="11" t="s">
+      <c r="E23" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="2">
         <v>0</v>
       </c>
       <c r="D24" s="3"/>
-      <c r="E24" s="14"/>
+      <c r="E24" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="2">
         <v>0</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="14"/>
+      <c r="E25" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="2">
         <v>0</v>
       </c>
       <c r="D26" s="3"/>
-      <c r="E26" s="14"/>
+      <c r="E26" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="2">
         <v>0</v>
       </c>
       <c r="D27" s="3"/>
-      <c r="E27" s="14"/>
+      <c r="E27" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="2">
         <v>0</v>
       </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="14"/>
+      <c r="E28" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="2">
         <v>0</v>
       </c>
       <c r="D29" s="3"/>
-      <c r="E29" s="14"/>
+      <c r="E29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5" customFormat="1" s="1">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="2">
         <v>0</v>
       </c>
       <c r="D30" s="3"/>
-      <c r="E30" s="14"/>
+      <c r="E30" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="2">
         <v>0</v>
       </c>
       <c r="D31" s="3"/>
-      <c r="E31" s="14"/>
+      <c r="E31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="2">
         <v>0</v>
       </c>
       <c r="D32" s="3"/>
-      <c r="E32" s="14"/>
+      <c r="E32" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1153,2633 +1132,2633 @@
   <dimension ref="A1:G175"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="16" width="23.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="16" width="24.14785714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="12" width="23.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="12" width="24.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A1" s="11" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5" customFormat="1" s="1">
+      <c r="A1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="13" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="14"/>
-      <c r="E2" s="13" t="s">
+      <c r="C2" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="13" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="13" t="s">
+      <c r="C3" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="13" t="s">
+      <c r="C4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="13" t="s">
+      <c r="C5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="13" t="s">
+      <c r="C6" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3"/>
+      <c r="E6" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="13" t="s">
+      <c r="C7" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="13" t="s">
+      <c r="C8" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="13" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
+      <c r="A9" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="13" t="s">
+      <c r="C9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
+      <c r="A10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="13" t="s">
+      <c r="C10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="13" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
+      <c r="A11" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="13" t="s">
+      <c r="C11" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="13" t="s">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
+      <c r="A12" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="13" t="s">
+      <c r="C12" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
+      <c r="A13" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="13" t="s">
+      <c r="C13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
+      <c r="A14" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="13" t="s">
+      <c r="C14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="14"/>
-      <c r="E15" s="13" t="s">
+      <c r="C15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="13" t="s">
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="13" t="s">
+      <c r="C16" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="13" t="s">
+      <c r="C17" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="13" t="s">
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="13" t="s">
+      <c r="C18" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="14"/>
-      <c r="E19" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="13" t="s">
+      <c r="C19" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="14"/>
-      <c r="E20" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="13" t="s">
+      <c r="C20" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="14"/>
-      <c r="E21" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="13" t="s">
+      <c r="C21" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="3"/>
+      <c r="E21" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+      <c r="A22" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="13" t="s">
+      <c r="C22" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="13" t="s">
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+      <c r="A23" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="13" t="s">
+      <c r="C23" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
+      <c r="A24" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" s="14"/>
-      <c r="E24" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="13" t="s">
+      <c r="C24" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
+      <c r="A25" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="14"/>
-      <c r="E25" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="13" t="s">
+      <c r="C25" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
+      <c r="A26" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="14"/>
-      <c r="E26" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="13" t="s">
+      <c r="C26" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
+      <c r="A27" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="14"/>
-      <c r="E27" s="13" t="s">
+      <c r="C27" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="13" t="s">
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
+      <c r="A28" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D28" s="14"/>
-      <c r="E28" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="13" t="s">
+      <c r="C28" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="3"/>
+      <c r="E28" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
+      <c r="A29" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="13" t="s">
+      <c r="C29" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
+      <c r="C30" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="3"/>
+      <c r="E30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D31" s="14"/>
-      <c r="E31" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
+      <c r="C31" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D32" s="14"/>
-      <c r="E32" s="13" t="s">
+      <c r="C32" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="13" t="s">
+      <c r="C33" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" s="3"/>
+      <c r="E33" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="13" t="s">
+      <c r="C34" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D35" s="14"/>
-      <c r="E35" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
+      <c r="C35" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="3"/>
+      <c r="E35" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D36" s="14"/>
-      <c r="E36" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
+      <c r="C36" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D37" s="14"/>
-      <c r="E37" s="13" t="s">
+      <c r="C37" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37" s="3"/>
+      <c r="E37" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" s="14"/>
-      <c r="E38" s="13" t="s">
+      <c r="C38" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C39" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D39" s="14"/>
-      <c r="E39" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
+      <c r="C39" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39" s="3"/>
+      <c r="E39" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B40" s="13" t="s">
+      <c r="B40" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D40" s="14"/>
-      <c r="E40" s="13" t="s">
+      <c r="C40" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40" s="3"/>
+      <c r="E40" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="13" t="s">
+      <c r="B41" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D41" s="14"/>
-      <c r="E41" s="13" t="s">
+      <c r="C41" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="3"/>
+      <c r="E41" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D42" s="14"/>
-      <c r="E42" s="13" t="s">
+      <c r="C42" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="3"/>
+      <c r="E42" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="13" t="s">
+      <c r="C43" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="3"/>
+      <c r="E43" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
+      <c r="C44" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44" s="3"/>
+      <c r="E44" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C45" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="13" t="s">
+      <c r="C45" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45" s="3"/>
+      <c r="E45" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C46" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
+      <c r="C46" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46" s="3"/>
+      <c r="E46" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B47" s="13" t="s">
+      <c r="B47" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C47" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
+      <c r="C47" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47" s="3"/>
+      <c r="E47" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D48" s="14"/>
-      <c r="E48" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
+      <c r="C48" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" s="3"/>
+      <c r="E48" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
+      <c r="C49" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49" s="3"/>
+      <c r="E49" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B50" s="13" t="s">
+      <c r="B50" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
+      <c r="C50" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
+      <c r="C51" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D51" s="3"/>
+      <c r="E51" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="B52" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D52" s="14"/>
-      <c r="E52" s="13" t="s">
+      <c r="C52" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D52" s="3"/>
+      <c r="E52" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="13" t="s">
+      <c r="A53" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="13" t="s">
+      <c r="B53" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C53" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D53" s="14"/>
-      <c r="E53" s="13" t="s">
+      <c r="C53" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D53" s="3"/>
+      <c r="E53" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B54" s="13" t="s">
+      <c r="B54" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D54" s="14"/>
-      <c r="E54" s="13" t="s">
+      <c r="C54" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D54" s="3"/>
+      <c r="E54" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B55" s="13" t="s">
+      <c r="B55" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C55" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D55" s="14"/>
-      <c r="E55" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
+      <c r="C55" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D55" s="3"/>
+      <c r="E55" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B56" s="13" t="s">
+      <c r="B56" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C56" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D56" s="14"/>
-      <c r="E56" s="13" t="s">
+      <c r="C56" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D56" s="3"/>
+      <c r="E56" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="13" t="s">
+      <c r="B57" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D57" s="14"/>
-      <c r="E57" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
+      <c r="C57" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D57" s="3"/>
+      <c r="E57" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
-      <c r="A58" s="13" t="s">
+      <c r="A58" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B58" s="13" t="s">
+      <c r="B58" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C58" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D58" s="14"/>
-      <c r="E58" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
+      <c r="C58" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D58" s="3"/>
+      <c r="E58" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B59" s="13" t="s">
+      <c r="B59" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C59" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D59" s="14"/>
-      <c r="E59" s="13" t="s">
+      <c r="C59" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B60" s="13" t="s">
+      <c r="B60" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C60" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D60" s="14"/>
-      <c r="E60" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
+      <c r="C60" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B61" s="13" t="s">
+      <c r="B61" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C61" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D61" s="14"/>
-      <c r="E61" s="13" t="s">
+      <c r="C61" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B62" s="13" t="s">
+      <c r="B62" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C62" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D62" s="14"/>
-      <c r="E62" s="13" t="s">
+      <c r="C62" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
-      <c r="A63" s="13" t="s">
+      <c r="A63" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B63" s="13" t="s">
+      <c r="B63" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C63" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D63" s="14"/>
-      <c r="E63" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
+      <c r="C63" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
-      <c r="A64" s="13" t="s">
+      <c r="A64" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B64" s="13" t="s">
+      <c r="B64" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C64" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D64" s="14"/>
-      <c r="E64" s="13" t="s">
+      <c r="C64" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B65" s="13" t="s">
+      <c r="B65" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C65" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D65" s="14"/>
-      <c r="E65" s="13" t="s">
+      <c r="C65" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
-      <c r="A66" s="13" t="s">
+      <c r="A66" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B66" s="13" t="s">
+      <c r="B66" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C66" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D66" s="14"/>
-      <c r="E66" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
+      <c r="C66" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B67" s="13" t="s">
+      <c r="B67" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C67" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D67" s="14"/>
-      <c r="E67" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
+      <c r="C67" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D67" s="3"/>
+      <c r="E67" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
-      <c r="A68" s="13" t="s">
+      <c r="A68" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B68" s="13" t="s">
+      <c r="B68" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C68" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D68" s="14"/>
-      <c r="E68" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
+      <c r="C68" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
-      <c r="A69" s="13" t="s">
+      <c r="A69" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B69" s="13" t="s">
+      <c r="B69" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C69" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D69" s="14"/>
-      <c r="E69" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F69" s="14"/>
-      <c r="G69" s="14"/>
+      <c r="C69" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B70" s="13" t="s">
+      <c r="B70" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D70" s="14"/>
-      <c r="E70" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F70" s="14"/>
-      <c r="G70" s="14"/>
+      <c r="C70" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
-      <c r="A71" s="13" t="s">
+      <c r="A71" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B71" s="13" t="s">
+      <c r="B71" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C71" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D71" s="14"/>
-      <c r="E71" s="13" t="s">
+      <c r="C71" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F71" s="14"/>
-      <c r="G71" s="14"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
-      <c r="A72" s="13" t="s">
+      <c r="A72" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B72" s="13" t="s">
+      <c r="B72" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D72" s="14"/>
-      <c r="E72" s="13" t="s">
+      <c r="C72" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
-      <c r="A73" s="13" t="s">
+      <c r="A73" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B73" s="13" t="s">
+      <c r="B73" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D73" s="14"/>
-      <c r="E73" s="13" t="s">
+      <c r="C73" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F73" s="14"/>
-      <c r="G73" s="14"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
-      <c r="A74" s="13" t="s">
+      <c r="A74" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B74" s="13" t="s">
+      <c r="B74" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D74" s="14"/>
-      <c r="E74" s="13" t="s">
+      <c r="C74" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F74" s="14"/>
-      <c r="G74" s="14"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
-      <c r="A75" s="13" t="s">
+      <c r="A75" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B75" s="13" t="s">
+      <c r="B75" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C75" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D75" s="14"/>
-      <c r="E75" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F75" s="14"/>
-      <c r="G75" s="14"/>
+      <c r="C75" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
-      <c r="A76" s="13" t="s">
+      <c r="A76" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B76" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C76" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D76" s="14"/>
-      <c r="E76" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F76" s="14"/>
-      <c r="G76" s="14"/>
+      <c r="C76" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D76" s="3"/>
+      <c r="E76" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
-      <c r="A77" s="13" t="s">
+      <c r="A77" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C77" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D77" s="14"/>
-      <c r="E77" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F77" s="14"/>
-      <c r="G77" s="14"/>
+      <c r="C77" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="C78" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D78" s="14"/>
-      <c r="E78" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F78" s="14"/>
-      <c r="G78" s="14"/>
+      <c r="C78" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
-      <c r="A79" s="13" t="s">
+      <c r="A79" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D79" s="14"/>
-      <c r="E79" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F79" s="14"/>
-      <c r="G79" s="14"/>
+      <c r="C79" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
-      <c r="A80" s="13" t="s">
+      <c r="A80" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D80" s="14"/>
-      <c r="E80" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
+      <c r="C80" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
-      <c r="A81" s="13" t="s">
+      <c r="A81" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D81" s="14"/>
-      <c r="E81" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
+      <c r="C81" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
-      <c r="A82" s="13" t="s">
+      <c r="A82" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D82" s="14"/>
-      <c r="E82" s="13" t="s">
+      <c r="C82" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D82" s="3"/>
+      <c r="E82" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
-      <c r="A83" s="13" t="s">
+      <c r="A83" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D83" s="14"/>
-      <c r="E83" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="14"/>
-      <c r="G83" s="14"/>
+      <c r="C83" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D83" s="3"/>
+      <c r="E83" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D84" s="14"/>
-      <c r="E84" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F84" s="14"/>
-      <c r="G84" s="14"/>
+      <c r="C84" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D84" s="3"/>
+      <c r="E84" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
-      <c r="A85" s="13" t="s">
+      <c r="A85" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="B85" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D85" s="14"/>
-      <c r="E85" s="13" t="s">
+      <c r="C85" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D85" s="3"/>
+      <c r="E85" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F85" s="14"/>
-      <c r="G85" s="14"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
-      <c r="A86" s="13" t="s">
+      <c r="A86" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D86" s="14"/>
-      <c r="E86" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F86" s="14"/>
-      <c r="G86" s="14"/>
+      <c r="C86" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D86" s="3"/>
+      <c r="E86" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
-      <c r="A87" s="13" t="s">
+      <c r="A87" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D87" s="14"/>
-      <c r="E87" s="13" t="s">
+      <c r="C87" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D87" s="3"/>
+      <c r="E87" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
-      <c r="A88" s="13" t="s">
+      <c r="A88" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D88" s="14"/>
-      <c r="E88" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
+      <c r="C88" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D88" s="3"/>
+      <c r="E88" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
-      <c r="A89" s="13" t="s">
+      <c r="A89" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D89" s="14"/>
-      <c r="E89" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F89" s="14"/>
-      <c r="G89" s="14"/>
+      <c r="C89" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D89" s="3"/>
+      <c r="E89" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
-      <c r="A90" s="13" t="s">
+      <c r="A90" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B90" s="13" t="s">
+      <c r="B90" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D90" s="14"/>
-      <c r="E90" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F90" s="14"/>
-      <c r="G90" s="14"/>
+      <c r="C90" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="E90" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
-      <c r="A91" s="13" t="s">
+      <c r="A91" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B91" s="13" t="s">
+      <c r="B91" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D91" s="14"/>
-      <c r="E91" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F91" s="14"/>
-      <c r="G91" s="14"/>
+      <c r="C91" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D91" s="3"/>
+      <c r="E91" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
-      <c r="A92" s="13" t="s">
+      <c r="A92" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="B92" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="C92" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D92" s="14"/>
-      <c r="E92" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
+      <c r="C92" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D92" s="3"/>
+      <c r="E92" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
-      <c r="A93" s="13" t="s">
+      <c r="A93" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C93" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D93" s="14"/>
-      <c r="E93" s="13" t="s">
+      <c r="C93" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D93" s="3"/>
+      <c r="E93" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F93" s="14"/>
-      <c r="G93" s="14"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C94" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D94" s="14"/>
-      <c r="E94" s="13" t="s">
+      <c r="C94" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D94" s="3"/>
+      <c r="E94" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F94" s="14"/>
-      <c r="G94" s="14"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
-      <c r="A95" s="13" t="s">
+      <c r="A95" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C95" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D95" s="14"/>
-      <c r="E95" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F95" s="14"/>
-      <c r="G95" s="14"/>
+      <c r="C95" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D95" s="3"/>
+      <c r="E95" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
-      <c r="A96" s="13" t="s">
+      <c r="A96" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C96" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D96" s="14"/>
-      <c r="E96" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F96" s="14"/>
-      <c r="G96" s="14"/>
+      <c r="C96" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D96" s="3"/>
+      <c r="E96" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
-      <c r="A97" s="13" t="s">
+      <c r="A97" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C97" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D97" s="14"/>
-      <c r="E97" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F97" s="14"/>
-      <c r="G97" s="14"/>
+      <c r="C97" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D97" s="3"/>
+      <c r="E97" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
-      <c r="A98" s="13" t="s">
+      <c r="A98" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B98" s="13" t="s">
+      <c r="B98" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C98" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D98" s="14"/>
-      <c r="E98" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F98" s="14"/>
-      <c r="G98" s="14"/>
+      <c r="C98" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D98" s="3"/>
+      <c r="E98" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
-      <c r="A99" s="13" t="s">
+      <c r="A99" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B99" s="13" t="s">
+      <c r="B99" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C99" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D99" s="14"/>
-      <c r="E99" s="13" t="s">
+      <c r="C99" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D99" s="3"/>
+      <c r="E99" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F99" s="14"/>
-      <c r="G99" s="14"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
-      <c r="A100" s="13" t="s">
+      <c r="A100" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B100" s="13" t="s">
+      <c r="B100" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C100" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D100" s="14"/>
-      <c r="E100" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F100" s="14"/>
-      <c r="G100" s="14"/>
+      <c r="C100" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D100" s="3"/>
+      <c r="E100" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B101" s="13" t="s">
+      <c r="B101" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C101" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D101" s="14"/>
-      <c r="E101" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F101" s="14"/>
-      <c r="G101" s="14"/>
+      <c r="C101" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D101" s="3"/>
+      <c r="E101" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
-      <c r="A102" s="13" t="s">
+      <c r="A102" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C102" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D102" s="14"/>
-      <c r="E102" s="13" t="s">
+      <c r="C102" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D102" s="3"/>
+      <c r="E102" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F102" s="14"/>
-      <c r="G102" s="14"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
-      <c r="A103" s="13" t="s">
+      <c r="A103" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B103" s="13" t="s">
+      <c r="B103" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D103" s="14"/>
-      <c r="E103" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F103" s="14"/>
-      <c r="G103" s="14"/>
+      <c r="C103" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D103" s="3"/>
+      <c r="E103" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B104" s="13" t="s">
+      <c r="B104" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D104" s="14"/>
-      <c r="E104" s="13" t="s">
+      <c r="C104" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D104" s="3"/>
+      <c r="E104" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F104" s="14"/>
-      <c r="G104" s="14"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
-      <c r="A105" s="13" t="s">
+      <c r="A105" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="B105" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D105" s="14"/>
-      <c r="E105" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F105" s="14"/>
-      <c r="G105" s="14"/>
+      <c r="C105" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D105" s="3"/>
+      <c r="E105" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
-      <c r="A106" s="13" t="s">
+      <c r="A106" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B106" s="13" t="s">
+      <c r="B106" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D106" s="14"/>
-      <c r="E106" s="13" t="s">
+      <c r="C106" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D106" s="3"/>
+      <c r="E106" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F106" s="14"/>
-      <c r="G106" s="14"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
-      <c r="A107" s="13" t="s">
+      <c r="A107" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B107" s="13" t="s">
+      <c r="B107" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C107" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D107" s="14"/>
-      <c r="E107" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F107" s="14"/>
-      <c r="G107" s="14"/>
+      <c r="C107" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D107" s="3"/>
+      <c r="E107" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
-      <c r="A108" s="13" t="s">
+      <c r="A108" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B108" s="13" t="s">
+      <c r="B108" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D108" s="14"/>
-      <c r="E108" s="13" t="s">
+      <c r="C108" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D108" s="3"/>
+      <c r="E108" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F108" s="14"/>
-      <c r="G108" s="14"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
-      <c r="A109" s="13" t="s">
+      <c r="A109" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B109" s="13" t="s">
+      <c r="B109" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C109" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D109" s="14"/>
-      <c r="E109" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F109" s="14"/>
-      <c r="G109" s="14"/>
+      <c r="C109" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D109" s="3"/>
+      <c r="E109" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
-      <c r="A110" s="13" t="s">
+      <c r="A110" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B110" s="13" t="s">
+      <c r="B110" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C110" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D110" s="14"/>
-      <c r="E110" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F110" s="14"/>
-      <c r="G110" s="14"/>
+      <c r="C110" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D110" s="3"/>
+      <c r="E110" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
-      <c r="A111" s="13" t="s">
+      <c r="A111" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B111" s="13" t="s">
+      <c r="B111" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D111" s="14"/>
-      <c r="E111" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F111" s="14"/>
-      <c r="G111" s="14"/>
+      <c r="C111" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D111" s="3"/>
+      <c r="E111" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
-      <c r="A112" s="13" t="s">
+      <c r="A112" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B112" s="13" t="s">
+      <c r="B112" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D112" s="14"/>
-      <c r="E112" s="13" t="s">
+      <c r="C112" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D112" s="3"/>
+      <c r="E112" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F112" s="14"/>
-      <c r="G112" s="14"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
-      <c r="A113" s="13" t="s">
+      <c r="A113" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="B113" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D113" s="14"/>
-      <c r="E113" s="13" t="s">
+      <c r="C113" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D113" s="3"/>
+      <c r="E113" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F113" s="14"/>
-      <c r="G113" s="14"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
-      <c r="A114" s="13" t="s">
+      <c r="A114" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B114" s="13" t="s">
+      <c r="B114" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D114" s="14"/>
-      <c r="E114" s="13" t="s">
+      <c r="C114" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D114" s="3"/>
+      <c r="E114" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F114" s="14"/>
-      <c r="G114" s="14"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
-      <c r="A115" s="13" t="s">
+      <c r="A115" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="B115" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C115" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D115" s="14"/>
-      <c r="E115" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F115" s="14"/>
-      <c r="G115" s="14"/>
+      <c r="C115" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D115" s="3"/>
+      <c r="E115" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
-      <c r="A116" s="13" t="s">
+      <c r="A116" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B116" s="13" t="s">
+      <c r="B116" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C116" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D116" s="14"/>
-      <c r="E116" s="13" t="s">
+      <c r="C116" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D116" s="3"/>
+      <c r="E116" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F116" s="14"/>
-      <c r="G116" s="14"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75">
-      <c r="A117" s="13" t="s">
+      <c r="A117" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="B117" s="13" t="s">
+      <c r="B117" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C117" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D117" s="14"/>
-      <c r="E117" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F117" s="14"/>
-      <c r="G117" s="14"/>
+      <c r="C117" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D117" s="3"/>
+      <c r="E117" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="118" customHeight="1" ht="18.75">
-      <c r="A118" s="13" t="s">
+      <c r="A118" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B118" s="13" t="s">
+      <c r="B118" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C118" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D118" s="14"/>
-      <c r="E118" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F118" s="14"/>
-      <c r="G118" s="14"/>
+      <c r="C118" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D118" s="3"/>
+      <c r="E118" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="119" customHeight="1" ht="18.75">
-      <c r="A119" s="13" t="s">
+      <c r="A119" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B119" s="13" t="s">
+      <c r="B119" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C119" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D119" s="14"/>
-      <c r="E119" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F119" s="14"/>
-      <c r="G119" s="14"/>
+      <c r="C119" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D119" s="3"/>
+      <c r="E119" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="120" customHeight="1" ht="18.75">
-      <c r="A120" s="13" t="s">
+      <c r="A120" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B120" s="13" t="s">
+      <c r="B120" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C120" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D120" s="14"/>
-      <c r="E120" s="13" t="s">
+      <c r="C120" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D120" s="3"/>
+      <c r="E120" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F120" s="14"/>
-      <c r="G120" s="14"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="121" customHeight="1" ht="18.75">
-      <c r="A121" s="13" t="s">
+      <c r="A121" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B121" s="13" t="s">
+      <c r="B121" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C121" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D121" s="14"/>
-      <c r="E121" s="13" t="s">
+      <c r="C121" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D121" s="3"/>
+      <c r="E121" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F121" s="14"/>
-      <c r="G121" s="14"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="122" customHeight="1" ht="18.75">
-      <c r="A122" s="13" t="s">
+      <c r="A122" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="B122" s="13" t="s">
+      <c r="B122" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C122" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D122" s="14"/>
-      <c r="E122" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F122" s="14"/>
-      <c r="G122" s="14"/>
+      <c r="C122" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D122" s="3"/>
+      <c r="E122" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F122" s="3"/>
+      <c r="G122" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="123" customHeight="1" ht="18.75">
-      <c r="A123" s="13" t="s">
+      <c r="A123" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B123" s="13" t="s">
+      <c r="B123" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C123" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D123" s="14"/>
-      <c r="E123" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F123" s="14"/>
-      <c r="G123" s="14"/>
+      <c r="C123" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D123" s="3"/>
+      <c r="E123" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F123" s="3"/>
+      <c r="G123" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="124" customHeight="1" ht="18.75">
-      <c r="A124" s="13" t="s">
+      <c r="A124" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B124" s="13" t="s">
+      <c r="B124" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D124" s="14"/>
-      <c r="E124" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F124" s="14"/>
-      <c r="G124" s="14"/>
+      <c r="C124" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D124" s="3"/>
+      <c r="E124" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F124" s="3"/>
+      <c r="G124" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="125" customHeight="1" ht="18.75">
-      <c r="A125" s="13" t="s">
+      <c r="A125" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B125" s="13" t="s">
+      <c r="B125" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C125" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D125" s="14"/>
-      <c r="E125" s="13" t="s">
+      <c r="C125" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D125" s="3"/>
+      <c r="E125" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F125" s="14"/>
-      <c r="G125" s="14"/>
+      <c r="F125" s="3"/>
+      <c r="G125" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="126" customHeight="1" ht="18.75">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B126" s="13" t="s">
+      <c r="B126" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C126" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D126" s="14"/>
-      <c r="E126" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F126" s="14"/>
-      <c r="G126" s="14"/>
+      <c r="C126" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D126" s="3"/>
+      <c r="E126" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F126" s="3"/>
+      <c r="G126" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="127" customHeight="1" ht="18.75">
-      <c r="A127" s="13" t="s">
+      <c r="A127" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B127" s="13" t="s">
+      <c r="B127" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C127" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D127" s="14"/>
-      <c r="E127" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F127" s="14"/>
-      <c r="G127" s="14"/>
+      <c r="C127" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D127" s="3"/>
+      <c r="E127" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F127" s="3"/>
+      <c r="G127" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="128" customHeight="1" ht="18.75">
-      <c r="A128" s="13" t="s">
+      <c r="A128" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B128" s="13" t="s">
+      <c r="B128" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C128" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D128" s="14"/>
-      <c r="E128" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F128" s="14"/>
-      <c r="G128" s="14"/>
+      <c r="C128" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D128" s="3"/>
+      <c r="E128" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F128" s="3"/>
+      <c r="G128" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="129" customHeight="1" ht="18.75">
-      <c r="A129" s="13" t="s">
+      <c r="A129" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B129" s="13" t="s">
+      <c r="B129" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C129" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D129" s="14"/>
-      <c r="E129" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F129" s="14"/>
-      <c r="G129" s="14"/>
+      <c r="C129" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D129" s="3"/>
+      <c r="E129" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F129" s="3"/>
+      <c r="G129" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="130" customHeight="1" ht="18.75">
-      <c r="A130" s="13" t="s">
+      <c r="A130" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B130" s="13" t="s">
+      <c r="B130" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C130" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D130" s="14"/>
-      <c r="E130" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F130" s="14"/>
-      <c r="G130" s="14"/>
+      <c r="C130" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D130" s="3"/>
+      <c r="E130" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F130" s="3"/>
+      <c r="G130" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="131" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A131" s="15"/>
-      <c r="B131" s="15"/>
-      <c r="C131" s="10"/>
+      <c r="A131" s="11"/>
+      <c r="B131" s="11"/>
+      <c r="C131" s="9"/>
       <c r="D131" s="3"/>
-      <c r="E131" s="15"/>
+      <c r="E131" s="11"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="132" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A132" s="15"/>
-      <c r="B132" s="15"/>
-      <c r="C132" s="10"/>
+      <c r="A132" s="11"/>
+      <c r="B132" s="11"/>
+      <c r="C132" s="9"/>
       <c r="D132" s="3"/>
-      <c r="E132" s="15"/>
+      <c r="E132" s="11"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="133" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A133" s="15"/>
-      <c r="B133" s="15"/>
-      <c r="C133" s="10"/>
+      <c r="A133" s="11"/>
+      <c r="B133" s="11"/>
+      <c r="C133" s="9"/>
       <c r="D133" s="3"/>
-      <c r="E133" s="15"/>
+      <c r="E133" s="11"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="134" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A134" s="15"/>
-      <c r="B134" s="15"/>
-      <c r="C134" s="10"/>
+      <c r="A134" s="11"/>
+      <c r="B134" s="11"/>
+      <c r="C134" s="9"/>
       <c r="D134" s="3"/>
-      <c r="E134" s="15"/>
+      <c r="E134" s="11"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="135" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A135" s="15"/>
-      <c r="B135" s="15"/>
-      <c r="C135" s="10"/>
+      <c r="A135" s="11"/>
+      <c r="B135" s="11"/>
+      <c r="C135" s="9"/>
       <c r="D135" s="3"/>
-      <c r="E135" s="15"/>
+      <c r="E135" s="11"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="136" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A136" s="15"/>
-      <c r="B136" s="15"/>
-      <c r="C136" s="10"/>
+      <c r="A136" s="11"/>
+      <c r="B136" s="11"/>
+      <c r="C136" s="9"/>
       <c r="D136" s="3"/>
-      <c r="E136" s="15"/>
+      <c r="E136" s="11"/>
       <c r="F136" s="3"/>
       <c r="G136" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="137" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A137" s="15"/>
-      <c r="B137" s="15"/>
-      <c r="C137" s="10"/>
+      <c r="A137" s="11"/>
+      <c r="B137" s="11"/>
+      <c r="C137" s="9"/>
       <c r="D137" s="3"/>
-      <c r="E137" s="15"/>
+      <c r="E137" s="11"/>
       <c r="F137" s="3"/>
       <c r="G137" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="138" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A138" s="15"/>
-      <c r="B138" s="15"/>
-      <c r="C138" s="10"/>
+      <c r="A138" s="11"/>
+      <c r="B138" s="11"/>
+      <c r="C138" s="9"/>
       <c r="D138" s="3"/>
-      <c r="E138" s="15"/>
+      <c r="E138" s="11"/>
       <c r="F138" s="3"/>
       <c r="G138" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="139" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A139" s="15"/>
-      <c r="B139" s="15"/>
-      <c r="C139" s="10"/>
+      <c r="A139" s="11"/>
+      <c r="B139" s="11"/>
+      <c r="C139" s="9"/>
       <c r="D139" s="3"/>
-      <c r="E139" s="15"/>
+      <c r="E139" s="11"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="140" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A140" s="15"/>
-      <c r="B140" s="15"/>
-      <c r="C140" s="10"/>
+      <c r="A140" s="11"/>
+      <c r="B140" s="11"/>
+      <c r="C140" s="9"/>
       <c r="D140" s="3"/>
-      <c r="E140" s="15"/>
+      <c r="E140" s="11"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="141" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A141" s="15"/>
-      <c r="B141" s="15"/>
-      <c r="C141" s="10"/>
+      <c r="A141" s="11"/>
+      <c r="B141" s="11"/>
+      <c r="C141" s="9"/>
       <c r="D141" s="3"/>
-      <c r="E141" s="15"/>
+      <c r="E141" s="11"/>
       <c r="F141" s="3"/>
       <c r="G141" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="142" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A142" s="15"/>
-      <c r="B142" s="15"/>
-      <c r="C142" s="10"/>
+      <c r="A142" s="11"/>
+      <c r="B142" s="11"/>
+      <c r="C142" s="9"/>
       <c r="D142" s="3"/>
-      <c r="E142" s="15"/>
+      <c r="E142" s="11"/>
       <c r="F142" s="3"/>
       <c r="G142" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="143" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A143" s="15"/>
-      <c r="B143" s="15"/>
-      <c r="C143" s="10"/>
+      <c r="A143" s="11"/>
+      <c r="B143" s="11"/>
+      <c r="C143" s="9"/>
       <c r="D143" s="3"/>
-      <c r="E143" s="15"/>
+      <c r="E143" s="11"/>
       <c r="F143" s="3"/>
       <c r="G143" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="144" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A144" s="15"/>
-      <c r="B144" s="15"/>
-      <c r="C144" s="10"/>
+      <c r="A144" s="11"/>
+      <c r="B144" s="11"/>
+      <c r="C144" s="9"/>
       <c r="D144" s="3"/>
-      <c r="E144" s="15"/>
+      <c r="E144" s="11"/>
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="145" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A145" s="15"/>
-      <c r="B145" s="15"/>
-      <c r="C145" s="10"/>
+      <c r="A145" s="11"/>
+      <c r="B145" s="11"/>
+      <c r="C145" s="9"/>
       <c r="D145" s="3"/>
-      <c r="E145" s="15"/>
+      <c r="E145" s="11"/>
       <c r="F145" s="3"/>
       <c r="G145" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="146" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A146" s="15"/>
-      <c r="B146" s="15"/>
-      <c r="C146" s="10"/>
+      <c r="A146" s="11"/>
+      <c r="B146" s="11"/>
+      <c r="C146" s="9"/>
       <c r="D146" s="3"/>
-      <c r="E146" s="15"/>
+      <c r="E146" s="11"/>
       <c r="F146" s="3"/>
       <c r="G146" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="147" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A147" s="15"/>
-      <c r="B147" s="15"/>
-      <c r="C147" s="10"/>
+      <c r="A147" s="11"/>
+      <c r="B147" s="11"/>
+      <c r="C147" s="9"/>
       <c r="D147" s="3"/>
-      <c r="E147" s="15"/>
+      <c r="E147" s="11"/>
       <c r="F147" s="3"/>
       <c r="G147" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="148" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A148" s="15"/>
-      <c r="B148" s="15"/>
-      <c r="C148" s="10"/>
+      <c r="A148" s="11"/>
+      <c r="B148" s="11"/>
+      <c r="C148" s="9"/>
       <c r="D148" s="3"/>
-      <c r="E148" s="15"/>
+      <c r="E148" s="11"/>
       <c r="F148" s="3"/>
       <c r="G148" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="149" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A149" s="15"/>
-      <c r="B149" s="15"/>
-      <c r="C149" s="10"/>
+      <c r="A149" s="11"/>
+      <c r="B149" s="11"/>
+      <c r="C149" s="9"/>
       <c r="D149" s="3"/>
-      <c r="E149" s="15"/>
+      <c r="E149" s="11"/>
       <c r="F149" s="3"/>
       <c r="G149" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="150" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A150" s="15"/>
-      <c r="B150" s="15"/>
-      <c r="C150" s="10"/>
+      <c r="A150" s="11"/>
+      <c r="B150" s="11"/>
+      <c r="C150" s="9"/>
       <c r="D150" s="3"/>
-      <c r="E150" s="15"/>
+      <c r="E150" s="11"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="151" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A151" s="15"/>
-      <c r="B151" s="15"/>
-      <c r="C151" s="10"/>
+      <c r="A151" s="11"/>
+      <c r="B151" s="11"/>
+      <c r="C151" s="9"/>
       <c r="D151" s="3"/>
-      <c r="E151" s="15"/>
+      <c r="E151" s="11"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="152" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A152" s="15"/>
-      <c r="B152" s="15"/>
-      <c r="C152" s="10"/>
+      <c r="A152" s="11"/>
+      <c r="B152" s="11"/>
+      <c r="C152" s="9"/>
       <c r="D152" s="3"/>
-      <c r="E152" s="15"/>
+      <c r="E152" s="11"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="153" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A153" s="15"/>
-      <c r="B153" s="15"/>
-      <c r="C153" s="10"/>
+      <c r="A153" s="11"/>
+      <c r="B153" s="11"/>
+      <c r="C153" s="9"/>
       <c r="D153" s="3"/>
-      <c r="E153" s="15"/>
+      <c r="E153" s="11"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="154" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A154" s="15"/>
-      <c r="B154" s="15"/>
-      <c r="C154" s="10"/>
+      <c r="A154" s="11"/>
+      <c r="B154" s="11"/>
+      <c r="C154" s="9"/>
       <c r="D154" s="3"/>
-      <c r="E154" s="15"/>
+      <c r="E154" s="11"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="155" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A155" s="15"/>
-      <c r="B155" s="15"/>
-      <c r="C155" s="10"/>
+      <c r="A155" s="11"/>
+      <c r="B155" s="11"/>
+      <c r="C155" s="9"/>
       <c r="D155" s="3"/>
-      <c r="E155" s="15"/>
+      <c r="E155" s="11"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="156" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A156" s="15"/>
-      <c r="B156" s="15"/>
-      <c r="C156" s="10"/>
+      <c r="A156" s="11"/>
+      <c r="B156" s="11"/>
+      <c r="C156" s="9"/>
       <c r="D156" s="3"/>
-      <c r="E156" s="15"/>
+      <c r="E156" s="11"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="157" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A157" s="15"/>
-      <c r="B157" s="15"/>
-      <c r="C157" s="10"/>
+      <c r="A157" s="11"/>
+      <c r="B157" s="11"/>
+      <c r="C157" s="9"/>
       <c r="D157" s="3"/>
-      <c r="E157" s="15"/>
+      <c r="E157" s="11"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="158" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A158" s="15"/>
-      <c r="B158" s="15"/>
-      <c r="C158" s="10"/>
+      <c r="A158" s="11"/>
+      <c r="B158" s="11"/>
+      <c r="C158" s="9"/>
       <c r="D158" s="3"/>
-      <c r="E158" s="15"/>
+      <c r="E158" s="11"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="159" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A159" s="15"/>
-      <c r="B159" s="15"/>
-      <c r="C159" s="10"/>
+      <c r="A159" s="11"/>
+      <c r="B159" s="11"/>
+      <c r="C159" s="9"/>
       <c r="D159" s="3"/>
-      <c r="E159" s="15"/>
+      <c r="E159" s="11"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="160" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A160" s="15"/>
-      <c r="B160" s="15"/>
-      <c r="C160" s="10"/>
+      <c r="A160" s="11"/>
+      <c r="B160" s="11"/>
+      <c r="C160" s="9"/>
       <c r="D160" s="3"/>
-      <c r="E160" s="15"/>
+      <c r="E160" s="11"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="161" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A161" s="15"/>
-      <c r="B161" s="15"/>
-      <c r="C161" s="10"/>
+      <c r="A161" s="11"/>
+      <c r="B161" s="11"/>
+      <c r="C161" s="9"/>
       <c r="D161" s="3"/>
-      <c r="E161" s="15"/>
+      <c r="E161" s="11"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="162" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A162" s="15"/>
-      <c r="B162" s="15"/>
-      <c r="C162" s="10"/>
+      <c r="A162" s="11"/>
+      <c r="B162" s="11"/>
+      <c r="C162" s="9"/>
       <c r="D162" s="3"/>
-      <c r="E162" s="15"/>
+      <c r="E162" s="11"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="163" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A163" s="15"/>
-      <c r="B163" s="15"/>
-      <c r="C163" s="10"/>
+      <c r="A163" s="11"/>
+      <c r="B163" s="11"/>
+      <c r="C163" s="9"/>
       <c r="D163" s="3"/>
-      <c r="E163" s="15"/>
+      <c r="E163" s="11"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="164" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A164" s="15"/>
-      <c r="B164" s="15"/>
-      <c r="C164" s="10"/>
+      <c r="A164" s="11"/>
+      <c r="B164" s="11"/>
+      <c r="C164" s="9"/>
       <c r="D164" s="3"/>
-      <c r="E164" s="15"/>
+      <c r="E164" s="11"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="165" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A165" s="15"/>
-      <c r="B165" s="15"/>
-      <c r="C165" s="10"/>
+      <c r="A165" s="11"/>
+      <c r="B165" s="11"/>
+      <c r="C165" s="9"/>
       <c r="D165" s="3"/>
-      <c r="E165" s="15"/>
+      <c r="E165" s="11"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="166" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A166" s="15"/>
-      <c r="B166" s="15"/>
-      <c r="C166" s="10"/>
+      <c r="A166" s="11"/>
+      <c r="B166" s="11"/>
+      <c r="C166" s="9"/>
       <c r="D166" s="3"/>
-      <c r="E166" s="15"/>
+      <c r="E166" s="11"/>
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="167" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A167" s="15"/>
-      <c r="B167" s="15"/>
-      <c r="C167" s="10"/>
+      <c r="A167" s="11"/>
+      <c r="B167" s="11"/>
+      <c r="C167" s="9"/>
       <c r="D167" s="3"/>
-      <c r="E167" s="15"/>
+      <c r="E167" s="11"/>
       <c r="F167" s="3"/>
       <c r="G167" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="168" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A168" s="15"/>
-      <c r="B168" s="15"/>
-      <c r="C168" s="10"/>
+      <c r="A168" s="11"/>
+      <c r="B168" s="11"/>
+      <c r="C168" s="9"/>
       <c r="D168" s="3"/>
-      <c r="E168" s="15"/>
+      <c r="E168" s="11"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="169" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A169" s="15"/>
-      <c r="B169" s="15"/>
-      <c r="C169" s="10"/>
+      <c r="A169" s="11"/>
+      <c r="B169" s="11"/>
+      <c r="C169" s="9"/>
       <c r="D169" s="3"/>
-      <c r="E169" s="15"/>
+      <c r="E169" s="11"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="170" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A170" s="15"/>
-      <c r="B170" s="15"/>
-      <c r="C170" s="10"/>
+      <c r="A170" s="11"/>
+      <c r="B170" s="11"/>
+      <c r="C170" s="9"/>
       <c r="D170" s="3"/>
-      <c r="E170" s="15"/>
+      <c r="E170" s="11"/>
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="171" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A171" s="15"/>
-      <c r="B171" s="15"/>
-      <c r="C171" s="10"/>
+      <c r="A171" s="11"/>
+      <c r="B171" s="11"/>
+      <c r="C171" s="9"/>
       <c r="D171" s="3"/>
-      <c r="E171" s="15"/>
+      <c r="E171" s="11"/>
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="172" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A172" s="15"/>
-      <c r="B172" s="15"/>
-      <c r="C172" s="10"/>
+      <c r="A172" s="11"/>
+      <c r="B172" s="11"/>
+      <c r="C172" s="9"/>
       <c r="D172" s="3"/>
-      <c r="E172" s="15"/>
+      <c r="E172" s="11"/>
       <c r="F172" s="3"/>
       <c r="G172" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="173" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A173" s="15"/>
-      <c r="B173" s="15"/>
-      <c r="C173" s="10"/>
+      <c r="A173" s="11"/>
+      <c r="B173" s="11"/>
+      <c r="C173" s="9"/>
       <c r="D173" s="3"/>
-      <c r="E173" s="15"/>
+      <c r="E173" s="11"/>
       <c r="F173" s="3"/>
       <c r="G173" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="174" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A174" s="15"/>
-      <c r="B174" s="15"/>
-      <c r="C174" s="10"/>
+      <c r="A174" s="11"/>
+      <c r="B174" s="11"/>
+      <c r="C174" s="9"/>
       <c r="D174" s="3"/>
-      <c r="E174" s="15"/>
+      <c r="E174" s="11"/>
       <c r="F174" s="3"/>
       <c r="G174" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="175" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A175" s="15"/>
-      <c r="B175" s="15"/>
-      <c r="C175" s="10"/>
+      <c r="A175" s="11"/>
+      <c r="B175" s="11"/>
+      <c r="C175" s="9"/>
       <c r="D175" s="3"/>
-      <c r="E175" s="15"/>
+      <c r="E175" s="11"/>
       <c r="F175" s="3"/>
       <c r="G175" s="3"/>
     </row>
@@ -3796,67 +3775,67 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="10"/>
+      <c r="D2" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A3" s="3"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A6" s="3"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75" customFormat="1" s="1">
       <c r="A7" s="3"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3871,9 +3850,9 @@
   <dimension ref="A1:C121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="8" width="23.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="32.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="7" width="23.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="32.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75" customFormat="1" s="1">
@@ -5101,7 +5080,7 @@
       <c r="C116" s="3"/>
     </row>
     <row x14ac:dyDescent="0.25" r="117" customHeight="1" ht="18.75" customFormat="1" s="1">
-      <c r="A117" s="7">
+      <c r="A117" s="2">
         <v>23</v>
       </c>
       <c r="B117" s="3"/>
